--- a/sheets/대금율보/검수/병신난봉가.xlsx
+++ b/sheets/대금율보/검수/병신난봉가.xlsx
@@ -4189,8 +4189,7 @@
         <is>
           <t xml:space="preserve">㴌
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -4202,8 +4201,7 @@
         <is>
           <t xml:space="preserve">㴌
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -4215,8 +4213,7 @@
         <is>
           <t xml:space="preserve">㴌
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
@@ -4228,8 +4225,7 @@
         <is>
           <t xml:space="preserve">㴌
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -4239,8 +4235,7 @@
       </c>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="K10" s="24" t="inlineStr">
@@ -4679,8 +4674,7 @@
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -4690,15 +4684,13 @@
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
@@ -4708,8 +4700,7 @@
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I18" s="24" t="inlineStr">
@@ -4719,8 +4710,7 @@
       </c>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K18" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/병신난봉가.xlsx
+++ b/sheets/대금율보/검수/병신난봉가.xlsx
@@ -3750,22 +3750,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
       <c r="J6" s="21"/>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4725,6 +4725,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>